--- a/01_MOS/01_MOS.xlsx
+++ b/01_MOS/01_MOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mixed_signal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8F1C8B-89D0-4E8F-96B7-498B8B6B183E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92858F8F-C215-47F6-82F0-0C22760A4CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,6 +265,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -368,17 +374,18 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -486,6 +493,44 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-65FF-411D-999E-3F11CACC30DE}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-65FF-411D-999E-3F11CACC30DE}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -855,6 +900,44 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-C6AB-4426-8315-7450D8D5251E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C6AB-4426-8315-7450D8D5251E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1223,6 +1306,44 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-C039-41A4-9B52-AFB7D183F5BB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C039-41A4-9B52-AFB7D183F5BB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1591,6 +1712,44 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-EED1-4C28-8590-760797FD50B3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EED1-4C28-8590-760797FD50B3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1870,6 +2029,1634 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>V_THP</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8AFC-4F3E-8FBE-59EE042E2CFF}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-8AFC-4F3E-8FBE-59EE042E2CFF}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>TT, 25C</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>FF,  -10C</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>SS, 110C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>FF, 110C</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>SS, -10C</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20u'!$I$1:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.49430000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.58830000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45760000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.39839999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.54910000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8AFC-4F3E-8FBE-59EE042E2CFF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1913801183"/>
+        <c:axId val="1913810783"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1913801183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913810783"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1913810783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913801183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>V_THN</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-2754-41CA-8A4F-F41B5B06BFEA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2754-41CA-8A4F-F41B5B06BFEA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>TT, 25C</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>FF,  -10C</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>SS, 110C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>FF, 110C</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>SS, -10C</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20u'!$J$1:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.3856</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.43269999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.34720000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29370000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43919999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2754-41CA-8A4F-F41B5B06BFEA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1913765663"/>
+        <c:axId val="1913760383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1913765663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913760383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1913760383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913765663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>KP_P</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-0EA1-4B4D-8C48-6EE0765F61F9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-0EA1-4B4D-8C48-6EE0765F61F9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>TT, 25C</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>FF,  -10C</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>SS, 110C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>FF, 110C</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>SS, -10C</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20u'!$I$7:$I$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>66.55</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>49.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>57.274999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57.274999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0EA1-4B4D-8C48-6EE0765F61F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1913786783"/>
+        <c:axId val="1913773823"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1913786783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913773823"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1913773823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913786783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>KP_N</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2A7B-4FFE-8597-A4CFEAFD3785}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-2A7B-4FFE-8597-A4CFEAFD3785}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>TT, 25C</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>FF,  -10C</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>SS, 110C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>FF, 110C</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>SS, -10C</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20u'!$J$7:$J$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>301.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>396.99999999999994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>183.15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>213.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>342.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2A7B-4FFE-8597-A4CFEAFD3785}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1913760863"/>
+        <c:axId val="1913772383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1913760863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913772383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1913772383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913760863"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1991,6 +3778,166 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -4042,6 +5989,2018 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
@@ -17693,6 +21652,150 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>421822</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>134258</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190050</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>85401</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FA75F6A-B50D-05EC-58E8-3FC2B6484200}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>430893</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>116114</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>199121</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>67257</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F725BE18-17BD-32B5-504F-4205AA7CE657}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>412751</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>97973</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>180979</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>49115</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D485177-C823-7293-EFC4-480C9E444EF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>430893</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>88899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>199121</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>40042</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="圖表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F12537DE-A048-9D3B-32B4-00D3910171D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -17967,11 +22070,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
@@ -17981,17 +22084,17 @@
       <c r="G1" s="1">
         <v>1.8</v>
       </c>
-      <c r="I1" s="19">
+      <c r="I1" s="13">
         <f>B6</f>
         <v>0.49430000000000002</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
@@ -18001,17 +22104,17 @@
       <c r="G2" s="1">
         <v>20</v>
       </c>
-      <c r="I2" s="19">
+      <c r="I2" s="13">
         <f>B18</f>
         <v>0.49</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
@@ -18021,7 +22124,7 @@
       <c r="G3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="13">
         <f>B30</f>
         <v>0.45760000000000001</v>
       </c>
@@ -18036,7 +22139,7 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="13">
         <f>B42</f>
         <v>0.39839999999999998</v>
       </c>
@@ -18051,7 +22154,7 @@
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="13">
         <f>B54</f>
         <v>0.54910000000000003</v>
       </c>
@@ -18075,7 +22178,7 @@
       <c r="G6" s="3">
         <v>0.38579999999999998</v>
       </c>
-      <c r="I6" s="19"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -18096,7 +22199,7 @@
       <c r="G7" s="3">
         <v>6.0210000000000003E-3</v>
       </c>
-      <c r="I7" s="19"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -18117,7 +22220,7 @@
       <c r="G8" s="3">
         <v>2.3309999999999998E-6</v>
       </c>
-      <c r="I8" s="19"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -18140,7 +22243,7 @@
         <f>10^(-3)/G8</f>
         <v>429.00042900042905</v>
       </c>
-      <c r="I9" s="19"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -18161,7 +22264,7 @@
       <c r="G10" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I10" s="19"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -18182,17 +22285,17 @@
       <c r="G11" s="3">
         <v>1.097E-13</v>
       </c>
-      <c r="I11" s="19"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I12" s="19"/>
+      <c r="I12" s="13"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
@@ -18202,14 +22305,14 @@
       <c r="G13" s="1">
         <v>1.8</v>
       </c>
-      <c r="I13" s="19"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
@@ -18219,14 +22322,14 @@
       <c r="G14" s="1">
         <v>20</v>
       </c>
-      <c r="I14" s="19"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
@@ -18236,7 +22339,7 @@
       <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="I15" s="19"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -18248,7 +22351,7 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="19"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -18260,7 +22363,7 @@
       <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I17" s="19"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -18281,7 +22384,7 @@
       <c r="G18" s="3">
         <v>0.38590000000000002</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="13">
         <f>C6</f>
         <v>0.38579999999999998</v>
       </c>
@@ -18305,7 +22408,7 @@
       <c r="G19" s="3">
         <v>7.9260000000000008E-3</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="13">
         <f>C18</f>
         <v>0.38590000000000002</v>
       </c>
@@ -18329,7 +22432,7 @@
       <c r="G20" s="3">
         <v>2.5739999999999998E-6</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="13">
         <f>C30</f>
         <v>0.34760000000000002</v>
       </c>
@@ -18355,7 +22458,7 @@
         <f>10^(-3)/G20</f>
         <v>388.50038850038851</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="13">
         <f>C42</f>
         <v>0.29399999999999998</v>
       </c>
@@ -18379,7 +22482,7 @@
       <c r="G22" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="13">
         <f>C54</f>
         <v>0.4395</v>
       </c>
@@ -18403,17 +22506,17 @@
       <c r="G23" s="3">
         <v>1.079E-13</v>
       </c>
-      <c r="I23" s="19"/>
+      <c r="I23" s="13"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I24" s="19"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
       <c r="E25" s="1" t="s">
         <v>17</v>
       </c>
@@ -18423,14 +22526,14 @@
       <c r="G25" s="1">
         <v>1.8</v>
       </c>
-      <c r="I25" s="19"/>
+      <c r="I25" s="13"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
       <c r="E26" s="1" t="s">
         <v>11</v>
       </c>
@@ -18440,14 +22543,14 @@
       <c r="G26" s="1">
         <v>20</v>
       </c>
-      <c r="I26" s="19"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
       <c r="E27" s="1" t="s">
         <v>12</v>
       </c>
@@ -18457,7 +22560,7 @@
       <c r="G27" s="1">
         <v>1</v>
       </c>
-      <c r="I27" s="19"/>
+      <c r="I27" s="13"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -18469,7 +22572,7 @@
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I28" s="19"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
@@ -18481,7 +22584,7 @@
       <c r="C29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="19"/>
+      <c r="I29" s="13"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -18502,7 +22605,7 @@
       <c r="G30" s="3">
         <v>0.34760000000000002</v>
       </c>
-      <c r="I30" s="19"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -18523,7 +22626,7 @@
       <c r="G31" s="3">
         <v>3.666E-3</v>
       </c>
-      <c r="I31" s="19"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -18544,7 +22647,7 @@
       <c r="G32" s="3">
         <v>1.9980000000000002E-6</v>
       </c>
-      <c r="I32" s="19"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -18567,7 +22670,7 @@
         <f>10^(-3)/G32</f>
         <v>500.50050050050049</v>
       </c>
-      <c r="I33" s="19"/>
+      <c r="I33" s="13"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -18588,7 +22691,7 @@
       <c r="G34" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I34" s="19"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -18609,17 +22712,17 @@
       <c r="G35" s="3">
         <v>1.149E-13</v>
       </c>
-      <c r="I35" s="19"/>
+      <c r="I35" s="13"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I36" s="19"/>
+      <c r="I36" s="13"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="16"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
       <c r="E37" s="1" t="s">
         <v>17</v>
       </c>
@@ -18629,17 +22732,17 @@
       <c r="G37" s="1">
         <v>1.8</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="13">
         <f>B7</f>
         <v>67.275000000000006</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="16"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
       <c r="E38" s="1" t="s">
         <v>11</v>
       </c>
@@ -18649,17 +22752,17 @@
       <c r="G38" s="1">
         <v>20</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="13">
         <f>B19</f>
         <v>80.474999999999994</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12"/>
       <c r="E39" s="1" t="s">
         <v>12</v>
       </c>
@@ -18669,7 +22772,7 @@
       <c r="G39" s="1">
         <v>1</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="13">
         <f>B31</f>
         <v>50.199999999999996</v>
       </c>
@@ -18684,7 +22787,7 @@
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="13">
         <f>B43</f>
         <v>58.125</v>
       </c>
@@ -18699,7 +22802,7 @@
       <c r="C41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="13">
         <f>B55</f>
         <v>70.05</v>
       </c>
@@ -18723,7 +22826,7 @@
       <c r="G42" s="3">
         <v>0.29399999999999998</v>
       </c>
-      <c r="I42" s="19"/>
+      <c r="I42" s="13"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -18744,7 +22847,7 @@
       <c r="G43" s="3">
         <v>4.2700000000000004E-3</v>
       </c>
-      <c r="I43" s="19"/>
+      <c r="I43" s="13"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -18765,7 +22868,7 @@
       <c r="G44" s="3">
         <v>2.2309999999999999E-6</v>
       </c>
-      <c r="I44" s="19"/>
+      <c r="I44" s="13"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -18788,7 +22891,7 @@
         <f>10^(-3)/G44</f>
         <v>448.22949350067239</v>
       </c>
-      <c r="I45" s="19"/>
+      <c r="I45" s="13"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
@@ -18809,7 +22912,7 @@
       <c r="G46" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I46" s="19"/>
+      <c r="I46" s="13"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
@@ -18830,17 +22933,17 @@
       <c r="G47" s="3">
         <v>1.128E-13</v>
       </c>
-      <c r="I47" s="19"/>
+      <c r="I47" s="13"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I48" s="19"/>
+      <c r="I48" s="13"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="16"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10"/>
       <c r="E49" s="1" t="s">
         <v>17</v>
       </c>
@@ -18850,17 +22953,17 @@
       <c r="G49" s="1">
         <v>1.8</v>
       </c>
-      <c r="I49" s="19">
+      <c r="I49" s="13">
         <f>C7</f>
         <v>301.05</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="16"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="10"/>
       <c r="E50" s="1" t="s">
         <v>11</v>
       </c>
@@ -18870,17 +22973,17 @@
       <c r="G50" s="1">
         <v>20</v>
       </c>
-      <c r="I50" s="19">
+      <c r="I50" s="13">
         <f>C19</f>
         <v>396.30000000000007</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
       <c r="E51" s="1" t="s">
         <v>12</v>
       </c>
@@ -18890,7 +22993,7 @@
       <c r="G51" s="1">
         <v>1</v>
       </c>
-      <c r="I51" s="19">
+      <c r="I51" s="13">
         <f>C31</f>
         <v>183.3</v>
       </c>
@@ -18905,7 +23008,7 @@
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I52" s="19">
+      <c r="I52" s="13">
         <f>C43</f>
         <v>213.5</v>
       </c>
@@ -18920,7 +23023,7 @@
       <c r="C53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I53" s="19">
+      <c r="I53" s="13">
         <f>C55</f>
         <v>342.4</v>
       </c>
@@ -19082,11 +23185,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
@@ -19096,13 +23199,21 @@
       <c r="G1" s="1">
         <v>1.8</v>
       </c>
+      <c r="I1" s="20">
+        <f>B6</f>
+        <v>0.49430000000000002</v>
+      </c>
+      <c r="J1" s="20">
+        <f>C6</f>
+        <v>0.3856</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
@@ -19112,13 +23223,21 @@
       <c r="G2" s="1">
         <v>20</v>
       </c>
+      <c r="I2" s="20">
+        <f>B18</f>
+        <v>0.58830000000000005</v>
+      </c>
+      <c r="J2" s="20">
+        <f>C18</f>
+        <v>0.43269999999999997</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
@@ -19127,6 +23246,14 @@
       </c>
       <c r="G3" s="1">
         <v>1</v>
+      </c>
+      <c r="I3" s="20">
+        <f>B30</f>
+        <v>0.45760000000000001</v>
+      </c>
+      <c r="J3" s="20">
+        <f>C30</f>
+        <v>0.34720000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -19139,6 +23266,14 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="I4" s="20">
+        <f>B42</f>
+        <v>0.39839999999999998</v>
+      </c>
+      <c r="J4" s="20">
+        <f>C42</f>
+        <v>0.29370000000000002</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -19150,6 +23285,14 @@
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="I5" s="20">
+        <f>B54</f>
+        <v>0.54910000000000003</v>
+      </c>
+      <c r="J5" s="20">
+        <f>C54</f>
+        <v>0.43919999999999998</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -19172,6 +23315,8 @@
       <c r="G6" s="3">
         <v>0.3856</v>
       </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -19192,6 +23337,14 @@
       <c r="G7" s="3">
         <v>6.0280000000000004E-3</v>
       </c>
+      <c r="I7" s="20">
+        <f>B7</f>
+        <v>66.55</v>
+      </c>
+      <c r="J7" s="20">
+        <f>C7</f>
+        <v>301.39999999999998</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -19212,6 +23365,14 @@
       <c r="G8" s="1">
         <v>4.0330000000000002E-6</v>
       </c>
+      <c r="I8" s="20">
+        <f>B19</f>
+        <v>79.7</v>
+      </c>
+      <c r="J8" s="20">
+        <f>C19</f>
+        <v>396.99999999999994</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -19234,6 +23395,14 @@
         <f>10^(-3)/G8</f>
         <v>247.95437639474335</v>
       </c>
+      <c r="I9" s="20">
+        <f>B31</f>
+        <v>49.5</v>
+      </c>
+      <c r="J9" s="20">
+        <f>C31</f>
+        <v>183.15</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -19254,6 +23423,14 @@
       <c r="G10" s="3">
         <v>2.0000000000000002E-5</v>
       </c>
+      <c r="I10" s="20">
+        <f>B43</f>
+        <v>57.274999999999999</v>
+      </c>
+      <c r="J10" s="20">
+        <f>C43</f>
+        <v>213.4</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -19274,6 +23451,14 @@
       <c r="G11" s="3">
         <v>1.295E-13</v>
       </c>
+      <c r="I11" s="20">
+        <f>B55</f>
+        <v>57.274999999999999</v>
+      </c>
+      <c r="J11" s="20">
+        <f>C55</f>
+        <v>342.9</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M12" t="s">
@@ -19281,11 +23466,11 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
@@ -19297,11 +23482,11 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="15"/>
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
@@ -19313,11 +23498,11 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
@@ -19473,11 +23658,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
       <c r="E25" s="1" t="s">
         <v>17</v>
       </c>
@@ -19489,11 +23674,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
       <c r="E26" s="1" t="s">
         <v>11</v>
       </c>
@@ -19505,11 +23690,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
       <c r="E27" s="1" t="s">
         <v>12</v>
       </c>
@@ -19665,11 +23850,11 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="10"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="19"/>
       <c r="E37" s="1" t="s">
         <v>17</v>
       </c>
@@ -19681,11 +23866,11 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="15"/>
       <c r="E38" s="1" t="s">
         <v>11</v>
       </c>
@@ -19697,11 +23882,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="17"/>
       <c r="E39" s="1" t="s">
         <v>12</v>
       </c>
@@ -19857,11 +24042,11 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="10"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="19"/>
       <c r="E49" s="1" t="s">
         <v>17</v>
       </c>
@@ -19873,11 +24058,11 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="15"/>
       <c r="E50" s="1" t="s">
         <v>11</v>
       </c>
@@ -19889,11 +24074,11 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="17"/>
       <c r="E51" s="1" t="s">
         <v>12</v>
       </c>
